--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -5068,7 +5068,7 @@
         <v>117884397</v>
       </c>
       <c r="B37" t="n">
-        <v>57828</v>
+        <v>57829</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -5072,7 +5072,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">

--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5194,6 +5194,130 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120425016</v>
+      </c>
+      <c r="B38" t="n">
+        <v>87380</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>809</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Praktvaxskivling</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hygrocybe splendidissima</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.D.Orton) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Muren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>560927</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6628566</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>5+1. Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Naturbetesmark med björk, En</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -5323,7 +5323,7 @@
         <v>120861608</v>
       </c>
       <c r="B39" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -5323,7 +5323,7 @@
         <v>120861608</v>
       </c>
       <c r="B39" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>

--- a/artfynd/A 65027-2023 artfynd.xlsx
+++ b/artfynd/A 65027-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4233,10 +4233,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>111940001</v>
+        <v>111940012</v>
       </c>
       <c r="B30" t="n">
-        <v>86475</v>
+        <v>85987</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4245,23 +4245,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4392</v>
+        <v>597</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ängsvaxskivling</t>
+          <t>Stornopping</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cuphophyllus pratensis s.lat.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Entoloma griseocyaneum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Kumm.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -4340,37 +4344,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>111939999</v>
+        <v>112577088</v>
       </c>
       <c r="B31" t="n">
-        <v>86266</v>
+        <v>91628</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4384</v>
+        <v>5966</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grå vaxskivling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gliophorus irrigatus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Pers.) A.M.Ainsw. &amp; P.M.Kirk</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4379,17 +4383,17 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Muren, Vstm</t>
+          <t>Skogen NV om beteshagen vid Skogsmuren, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>560927</v>
+        <v>560869</v>
       </c>
       <c r="R31" t="n">
-        <v>6628566</v>
+        <v>6628833</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4413,12 +4417,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Lagt in miljöbilder då även denna skog kommer stt försvinna pga slutavverkning</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4431,30 +4440,35 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Naturbetesmark med björk</t>
+          <t>Tallhällmarkskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>111940012</v>
+        <v>112577440</v>
       </c>
       <c r="B32" t="n">
-        <v>85987</v>
+        <v>91055</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4467,21 +4481,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>597</v>
+        <v>5966</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stornopping</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Entoloma griseocyaneum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4490,17 +4504,17 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Muren, Vstm</t>
+          <t>Skogen NV om beteshagen Skogsmuren, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>560927</v>
+        <v>560851</v>
       </c>
       <c r="R32" t="n">
-        <v>6628566</v>
+        <v>6628866</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4524,12 +4538,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2023-10-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Lagt in miljöbilder då även denna skog kommer att försvinna pga slutavverkning</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4542,34 +4561,39 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Naturbetesmark med björk</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112577088</v>
+        <v>112921655</v>
       </c>
       <c r="B33" t="n">
-        <v>91628</v>
+        <v>56781</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4578,40 +4602,49 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skogen NV om beteshagen vid Skogsmuren, Ramnäs, Vstm, Vstm</t>
+          <t>Ulvramenskogen, Ramnäs sn, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>560869</v>
+        <v>560743</v>
       </c>
       <c r="R33" t="n">
-        <v>6628833</v>
+        <v>6628677</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4635,17 +4668,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Lagt in miljöbilder då även denna skog kommer stt försvinna pga slutavverkning</t>
+          <t>På granar med barkborreangepp.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4654,85 +4697,91 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Tallhällmarkskog</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Sören Larsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112577440</v>
+        <v>113211608</v>
       </c>
       <c r="B34" t="n">
-        <v>91055</v>
+        <v>56323</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5966</v>
+        <v>100045</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>sträckande V</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogen NV om beteshagen Skogsmuren, Ramnäs, Vstm, Vstm</t>
+          <t>Skogsmuren, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>560851</v>
+        <v>560801</v>
       </c>
       <c r="R34" t="n">
-        <v>6628866</v>
+        <v>6628608</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4756,17 +4805,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Lagt in miljöbilder då även denna skog kommer att försvinna pga slutavverkning</t>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4775,19 +4829,8 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4804,10 +4847,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112921655</v>
+        <v>117884397</v>
       </c>
       <c r="B35" t="n">
-        <v>56781</v>
+        <v>57831</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4816,20 +4859,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>102990</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4842,27 +4885,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ulvramenskogen, Ramnäs sn, Vstm</t>
+          <t>Skogsmuren, Ramnäs (A 65027-2023, Skogsmuren), Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>560743</v>
+        <v>560826</v>
       </c>
       <c r="R35" t="n">
-        <v>6628677</v>
+        <v>6628550</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4886,27 +4931,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På granar med barkborreangepp.</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4917,26 +4957,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sören Larsson</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113211608</v>
+        <v>120861608</v>
       </c>
       <c r="B36" t="n">
-        <v>56323</v>
+        <v>57370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4945,20 +4990,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100045</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4968,18 +5013,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>sträckande V</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4989,17 +5030,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skogsmuren, Ramnäs, Vstm, Vstm</t>
+          <t>Skogen NV om Skogsmuren, Skogen NV om Skogsmuren, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>560801</v>
+        <v>560686</v>
       </c>
       <c r="R36" t="n">
-        <v>6628608</v>
+        <v>6628642</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5023,22 +5064,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gysinge skog dikar med grävmaskin i skogen intill naturreservatet, spillkråkan flyger fram och tillbaka i närheten, är orolig och ropar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5062,394 +5108,6 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>117884397</v>
-      </c>
-      <c r="B37" t="n">
-        <v>57831</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>102990</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Järnsparv</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Prunella modularis</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Skogsmuren, Ramnäs (A 65027-2023, Skogsmuren), Vstm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>560826</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6628550</v>
-      </c>
-      <c r="S37" t="n">
-        <v>50</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Öppen fastmark - med eller utan enstaka träd</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>120425016</v>
-      </c>
-      <c r="B38" t="n">
-        <v>88455</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>809</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Praktvaxskivling</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Hygrocybe splendidissima</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(P.D.Orton) M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Muren, Vstm</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>560927</v>
-      </c>
-      <c r="R38" t="n">
-        <v>6628566</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2024-10-15</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>5+1. Återfynd.</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Naturbetesmark med björk, En</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Tom Sävström</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>120861608</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57370</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Skogen NV om Skogsmuren, Skogen NV om Skogsmuren, Vstm</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>560686</v>
-      </c>
-      <c r="R39" t="n">
-        <v>6628642</v>
-      </c>
-      <c r="S39" t="n">
-        <v>50</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Surahammar</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Ramnäs</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gysinge skog dikar med grävmaskin i skogen intill naturreservatet, spillkråkan flyger fram och tillbaka i närheten, är orolig och ropar.</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
